--- a/תפקידים-וסיכויים.xlsx
+++ b/תפקידים-וסיכויים.xlsx
@@ -2742,7 +2742,7 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>מנהלה מרכזית</t>
+          <t>מנהלה מקצועית</t>
         </is>
       </c>
       <c r="D35" s="11" t="n">
